--- a/kerntabellen/gemeente_streekwerking.xlsx
+++ b/kerntabellen/gemeente_streekwerking.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\gebiedsniveaus\kerntabellen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE564873-D60F-484C-BE18-887D31F13783}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD8CB27C-6568-43F5-8F7D-77F0E1D0A941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-4065" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Blad1" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Blad1!$A$1:$D$288</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4894,7 +4894,7 @@
         <v>331</v>
       </c>
       <c r="C248" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="D248" t="s">
         <v>285</v>
@@ -5461,7 +5461,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1" xr:uid="{FFAD801E-B6D7-47B0-A1DC-983DE19EAB1A}">
+  <autoFilter ref="A1:D288" xr:uid="{FFAD801E-B6D7-47B0-A1DC-983DE19EAB1A}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D289">
       <sortCondition ref="A1"/>
     </sortState>
